--- a/vault/30_관계자인터뷰/AX기획팀/대구석FGI_내부부서_사전인터뷰_결과요약_국디마보고용_1026.xlsx
+++ b/vault/30_관계자인터뷰/AX기획팀/대구석FGI_내부부서_사전인터뷰_결과요약_국디마보고용_1026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82109\Desktop\2026\대구석\착수보고준비\착수보고 이후\내부인터뷰_준비\내부인터뷰자료취합_최종\내부인터뷰 취합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\뉴프로젝트\2026dgs\vault\30_관계자인터뷰\AX기획팀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1747A2-C3E8-4F57-89C7-AD06CE207C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4CF81A-8CCC-4823-852D-6F2CE51A2E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1605" windowWidth="29040" windowHeight="15840" tabRatio="905" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_요약" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="476">
   <si>
     <t>국내디지털마케팅팀 협의·확인 요청사항 및 후속 일정(안)</t>
   </si>
@@ -217,34 +217,22 @@
     <t>대면 인터뷰 결과와 추가 협의·확인사항을 정리하여 국디마팀·AX팀 공유</t>
   </si>
   <si>
-    <t>10. 29.~30.</t>
-  </si>
-  <si>
     <t>결과 요약·확인사항 목록</t>
   </si>
   <si>
     <t>예비가설·FGI 설명자료·사용자 및 업계 문항 보완(기존 문항 번호 대조)</t>
   </si>
   <si>
-    <t>10. 30.~11. 3.</t>
-  </si>
-  <si>
     <t>조사 설계 보완본</t>
   </si>
   <si>
     <t>업계 FGI: 기협업 경험·개선 요구 및 신규 협업 가능성·참여 조건 탐색</t>
   </si>
   <si>
-    <t>11월 1주(안)</t>
-  </si>
-  <si>
     <t>참여자·질문지 확정 후 진행. 회차별 요약·분석</t>
   </si>
   <si>
     <t>사용자 FGI: 서비스 이용 연속성·여행 단계별 기대·정보 신뢰 조건 확인</t>
-  </si>
-  <si>
-    <t>11.19.~20.(안)</t>
   </si>
   <si>
     <t>모집·분류 확정 후 진행. 회차별 요약·분석</t>
@@ -1519,11 +1507,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">• [핵심] 초기 여행비서가 이용자의 여행 준비과정에서 어던 도움을 주는 모습을 구상하고 계신가요? 사례로 말씀해주셔도 됩니다. 
-- [프로브] 여행 중 도움에 대한 의견도 이번 FGI에서 확인할 필요가 있을까요? 있다면 어떤 상황을 우선 살펴보면 좋을까요? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- 여행 전, 중 실제 어려움을 먼저 묻고, 향후 서비스에 대한 기대는 별도로 수집할 예정. 시민참여단의 자료는 추가 탐색의 단서로만 활용하고, 개발일정에 대한 확답은 요구하지 않도록 함</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1581,15 +1564,6 @@
     <t>D. 민간 제휴·정보신뢰 
 - 사용자: 추천을 믿고 선택한 경험/ 제휴 광고 정보의 수용/ 공공 플랫폼에 대한 기대
 - 업계: 협업 가치와 신뢰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">• [핵심] 제휴나 홍보 정보가 함께 안내될 때 이용자가 무엇을 알고 판단할 수 있어야 한다고 보시나요? 
-- [프로브] 출처, 추천 이유, 제휴 여부 등에 관해 이용자가 어던 정보를 필요로 하는지 FGI에서 확인하면 도움이 될까요?
-• [핵심] 시민참여단 자문에서는 추천 이유와 광고·제휴 여부를 알 수 있어야 한다는 의견과, 특정 업체 중심의 추천이 공공플랫폼의 신뢰를 떨어뜨릴 수 있다는 우려가 제시됐습니다. 이와 관련해 이번 FGI에서 이용자의 어떤 판단이나 반응을 우선 확인하면 도움이 될까요?
-- [프로브] 예를 들어 추천 이유를 알면 더 도움이 되는지, 또는 제휴 정보라는 사실을 알았을 때 신뢰와 이용 의향이 달라지는지 중 우선 살펴볼 부분이 있을까요? 다른 쟁점을 생각하고 있다면 말씀해 주세요.
-- [프로브] 관광지 안내에 숙박·체험상품이나 할인 혜택이 함께 제시되는 등, 이 문제를 살펴보기 좋은 이용 상황을 하나 말씀해 주실 수 있을까요?
-</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1744,6 +1718,48 @@
     <t>국내디지털마케팅팀 → 관광AX기획팀 전달용 · 테마관 운영부서 서면 의견조사(2026. 10) 기준 · 운영부서 3곳 회신 · 부서명 비기재  ※ 작성: 투어리즘인사이트(2026. 10. 26.)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">• [핵심] 제휴나 홍보 정보가 함께 안내될 때 이용자가 무엇을 알고 판단할 수 있어야 한다고 보시나요? 
+- [프로브] 출처, 추천 이유, 제휴 여부 등에 관해 이용자가 어떤 정보를 필요로 하는지 FGI에서 확인하면 도움이 될까요?
+• [핵심] 시민참여단 자문에서는 추천 이유와 광고·제휴 여부를 알 수 있어야 한다는 의견과, 특정 업체 중심의 추천이 공공플랫폼의 신뢰를 떨어뜨릴 수 있다는 우려가 제시됐습니다. 이와 관련해 이번 FGI에서 이용자의 어떤 판단이나 반응을 우선 확인하면 도움이 될까요?
+- [프로브] 예를 들어 추천 이유를 알면 더 도움이 되는지, 또는 제휴 정보라는 사실을 알았을 때 신뢰와 이용 의향이 달라지는지 중 우선 살펴볼 부분이 있을까요? 다른 쟁점을 생각하고 있다면 말씀해 주세요.
+- [프로브] 관광지 안내에 숙박·체험상품이나 할인 혜택이 함께 제시되는 등, 이 문제를 살펴보기 좋은 이용 상황을 하나 말씀해 주실 수 있을까요?
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">• [핵심] 초기 여행비서가 이용자의 여행 준비과정에서 어떤 도움을 주는 모습을 구상하고 계신가요? 사례로 말씀해주셔도 됩니다. 
+- [프로브] 여행 중 도움에 대한 의견도 이번 FGI에서 확인할 필요가 있을까요? 있다면 어떤 상황을 우선 살펴보면 좋을까요? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> B-1 질문 제외</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI를 활용한 여행 플래닝 기능이 포함되는지로 질문 변경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>협업체에 대한 정보 제공이나 협업 주체별 챗봇 정보 제공을 위한 "공급자" 입장에서의 준비 사항 질문 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.19(목)~20(금)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. 11(수)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10. 29(목)~30(금)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10. 30(금)~11. 3(화)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1753,7 +1769,7 @@
     <numFmt numFmtId="176" formatCode="\•\ @"/>
     <numFmt numFmtId="177" formatCode="\-\ @"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2064,6 +2080,15 @@
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -2407,7 +2432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2566,44 +2591,143 @@
     <xf numFmtId="0" fontId="37" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="21" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2616,10 +2740,11 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2627,13 +2752,13 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2661,119 +2786,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="21" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3070,158 +3088,158 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="15.9140625" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="47" customHeight="1">
-      <c r="A1" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-    </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1">
-      <c r="A2" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
+    <row r="1" spans="1:3" ht="47.1" customHeight="1">
+      <c r="A1" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+    </row>
+    <row r="2" spans="1:3" ht="21.95" customHeight="1">
+      <c r="A2" s="96" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
     </row>
     <row r="3" spans="1:3" ht="6" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3" ht="34" customHeight="1">
-      <c r="A4" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
+    <row r="4" spans="1:3" ht="33.950000000000003" customHeight="1">
+      <c r="A4" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="65"/>
-    </row>
-    <row r="6" spans="1:3" ht="37" customHeight="1">
+        <v>65</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="90"/>
+    </row>
+    <row r="6" spans="1:3" ht="36.950000000000003" customHeight="1">
       <c r="A6" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="65"/>
+        <v>67</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="90"/>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1">
       <c r="A7" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="65"/>
+        <v>69</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="90"/>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
       <c r="A8" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="65"/>
-    </row>
-    <row r="9" spans="1:3" ht="64" customHeight="1">
+        <v>71</v>
+      </c>
+      <c r="B8" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="90"/>
+    </row>
+    <row r="9" spans="1:3" ht="63.95" customHeight="1">
       <c r="A9" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>452</v>
-      </c>
-      <c r="C9" s="65"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" s="90"/>
     </row>
     <row r="10" spans="1:3" ht="6" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="34" customHeight="1">
-      <c r="A11" s="67" t="s">
+    <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1">
+      <c r="A11" s="92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+    </row>
+    <row r="12" spans="1:3" ht="26.1" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="66.95" customHeight="1">
+      <c r="A13" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-    </row>
-    <row r="12" spans="1:3" ht="26" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="48" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="5" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="66.95" customHeight="1">
+      <c r="A14" s="95"/>
+      <c r="B14" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C14" s="48" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="67" customHeight="1">
-      <c r="A13" s="68" t="s">
+    <row r="15" spans="1:3" ht="66.95" customHeight="1">
+      <c r="A15" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="48" t="s">
-        <v>420</v>
-      </c>
-      <c r="C13" s="48" t="s">
+      <c r="B15" s="48" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="67" customHeight="1">
-      <c r="A14" s="69"/>
-      <c r="B14" s="48" t="s">
+      <c r="C15" s="48" t="s">
         <v>84</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="67" customHeight="1">
-      <c r="A15" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="52.5" customHeight="1">
       <c r="A16" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="90.95" customHeight="1">
+      <c r="A17" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="C17" s="48" t="s">
         <v>90</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="91" customHeight="1">
-      <c r="A17" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1">
@@ -3230,64 +3248,73 @@
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="49.5" customHeight="1">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+    </row>
+    <row r="20" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A20" s="89" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="91"/>
+      <c r="C20" s="90"/>
+    </row>
+    <row r="21" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A21" s="89" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="91"/>
+      <c r="C21" s="90"/>
+    </row>
+    <row r="22" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A22" s="89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="91"/>
+      <c r="C22" s="90"/>
+    </row>
+    <row r="23" spans="1:3" ht="36.950000000000003" customHeight="1">
+      <c r="A23" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-    </row>
-    <row r="20" spans="1:3" ht="25" customHeight="1">
-      <c r="A20" s="63" t="s">
+      <c r="B23" s="91"/>
+      <c r="C23" s="90"/>
+    </row>
+    <row r="24" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A24" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-    </row>
-    <row r="21" spans="1:3" ht="25" customHeight="1">
-      <c r="A21" s="63" t="s">
+      <c r="B24" s="91"/>
+      <c r="C24" s="90"/>
+    </row>
+    <row r="25" spans="1:3" ht="36.950000000000003" customHeight="1">
+      <c r="A25" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-    </row>
-    <row r="22" spans="1:3" ht="25" customHeight="1">
-      <c r="A22" s="63" t="s">
+      <c r="B25" s="91"/>
+      <c r="C25" s="90"/>
+    </row>
+    <row r="26" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A26" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-    </row>
-    <row r="23" spans="1:3" ht="37" customHeight="1">
-      <c r="A23" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-    </row>
-    <row r="24" spans="1:3" ht="25" customHeight="1">
-      <c r="A24" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-    </row>
-    <row r="25" spans="1:3" ht="37" customHeight="1">
-      <c r="A25" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-    </row>
-    <row r="26" spans="1:3" ht="25" customHeight="1">
-      <c r="A26" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="65"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="90"/>
     </row>
     <row r="27" spans="1:3" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A22:C22"/>
@@ -3297,15 +3324,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3319,233 +3337,233 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="66.08203125" customWidth="1"/>
+    <col min="3" max="3" width="66.125" customWidth="1"/>
     <col min="4" max="4" width="58" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.15" customHeight="1">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A1" s="124" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="132"/>
+    </row>
+    <row r="3" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A3" s="125" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="132"/>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="122" t="s">
+        <v>364</v>
+      </c>
+      <c r="B4" s="123"/>
+      <c r="C4" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="122" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="98"/>
-    </row>
-    <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="91" t="s">
+      <c r="B5" s="123"/>
+      <c r="C5" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="98"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="88" t="s">
-        <v>368</v>
-      </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="16" t="s">
+      <c r="D5" s="32" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="122" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="123"/>
+      <c r="C6" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="D4" s="32" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="D6" s="32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="122" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="16" t="s">
+      <c r="B7" s="123"/>
+      <c r="C7" s="16" t="s">
         <v>371</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="A6" s="88" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="A7" s="88" t="s">
-        <v>374</v>
-      </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="16" t="s">
-        <v>375</v>
       </c>
       <c r="D7" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="88" t="s">
-        <v>377</v>
-      </c>
-      <c r="B8" s="89"/>
+      <c r="A8" s="122" t="s">
+        <v>373</v>
+      </c>
+      <c r="B8" s="123"/>
       <c r="C8" s="16" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D8" s="32">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="20.149999999999999" customHeight="1">
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22" customHeight="1">
-      <c r="A11" s="91" t="s">
-        <v>380</v>
-      </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="98"/>
-    </row>
-    <row r="12" spans="1:4" ht="95.15" customHeight="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A11" s="125" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="132"/>
+    </row>
+    <row r="12" spans="1:4" ht="95.1" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D12" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="65.150000000000006" customHeight="1">
+    <row r="13" spans="1:4" ht="65.099999999999994" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A14" s="125" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="132"/>
+    </row>
+    <row r="15" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A15" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="B15" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>384</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="22" customHeight="1">
-      <c r="A14" s="91" t="s">
-        <v>386</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="98"/>
-    </row>
-    <row r="15" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A15" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>388</v>
       </c>
       <c r="D15" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="65.150000000000006" customHeight="1">
+    <row r="16" spans="1:4" ht="65.099999999999994" customHeight="1">
       <c r="A16" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A17" s="125" t="s">
         <v>390</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="132"/>
+    </row>
+    <row r="18" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C18" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="22" customHeight="1">
-      <c r="A17" s="91" t="s">
+      <c r="D18" s="33" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A19" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="98"/>
-    </row>
-    <row r="18" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A18" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="19" t="s">
+      <c r="B19" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C19" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A19" s="18" t="s">
+      <c r="D19" s="34" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="138.94999999999999" customHeight="1">
+      <c r="A20" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="C20" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="139" customHeight="1">
-      <c r="A20" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>403</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="87" t="s">
-        <v>405</v>
-      </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="98"/>
+      <c r="A22" s="121" t="s">
+        <v>401</v>
+      </c>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3572,508 +3590,521 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="17"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
     <col min="3" max="3" width="34" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="35.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="59.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="59.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="14" style="2" customWidth="1"/>
     <col min="8" max="16384" width="14" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="47.5" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="22" customHeight="1">
-      <c r="A2" s="56" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="47.45" customHeight="1">
+      <c r="A1" s="105" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="6" customHeight="1"/>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="62"/>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="64" customHeight="1">
-      <c r="A5" s="101" t="s">
-        <v>430</v>
-      </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="6" customHeight="1"/>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="106" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="101"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="63.95" customHeight="1">
+      <c r="A5" s="103" t="s">
+        <v>426</v>
+      </c>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="39" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="98.1" customHeight="1">
+      <c r="A7" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D7" s="63" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="F7" s="65" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="66" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="155.44999999999999" customHeight="1" thickBot="1">
+      <c r="A8" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>419</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>468</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="83.45" customHeight="1" thickTop="1">
+      <c r="A9" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="77" t="s">
+        <v>431</v>
+      </c>
+      <c r="G9" s="78" t="s">
+        <v>432</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="211.5" customHeight="1">
+      <c r="A10" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="63" t="s">
         <v>421</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="E10" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="79" t="s">
+        <v>434</v>
+      </c>
+      <c r="G10" s="66" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" ht="144.94999999999999" customHeight="1" thickBot="1">
+      <c r="A11" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="G11" s="80"/>
+      <c r="H11" s="134" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" ht="144.94999999999999" customHeight="1" thickTop="1">
+      <c r="A12" s="73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="75" t="s">
         <v>422</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="98" customHeight="1">
-      <c r="A7" s="107" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="108" t="s">
+      <c r="E12" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="86" t="s">
+        <v>436</v>
+      </c>
+      <c r="G12" s="78" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" ht="131.44999999999999" customHeight="1" thickBot="1">
+      <c r="A13" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="237" customHeight="1" thickTop="1">
+      <c r="A14" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="84" t="s">
+        <v>467</v>
+      </c>
+      <c r="G14" s="82" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" ht="142.5" customHeight="1" thickBot="1">
+      <c r="A15" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="E15" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="109" t="s">
-        <v>424</v>
-      </c>
-      <c r="E7" s="110" t="s">
-        <v>110</v>
-      </c>
-      <c r="F7" s="111" t="s">
-        <v>435</v>
-      </c>
-      <c r="G7" s="112" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="155.5" customHeight="1" thickBot="1">
-      <c r="A8" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="114" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="114" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="115" t="s">
-        <v>423</v>
-      </c>
-      <c r="E8" s="116" t="s">
+      <c r="F15" s="71" t="s">
+        <v>442</v>
+      </c>
+      <c r="G15" s="72"/>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" ht="336" customHeight="1" thickTop="1">
+      <c r="A16" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="F8" s="117" t="s">
-        <v>433</v>
-      </c>
-      <c r="G8" s="118" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="83.5" customHeight="1" thickTop="1">
-      <c r="A9" s="119" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="120" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="121" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="122" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="123" t="s">
-        <v>436</v>
-      </c>
-      <c r="G9" s="124" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="211.5" customHeight="1">
-      <c r="A10" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="108" t="s">
+      <c r="E16" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>443</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A17" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>444</v>
+      </c>
+      <c r="G17" s="57"/>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" ht="216" customHeight="1">
+      <c r="A18" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" ht="175.5" customHeight="1">
+      <c r="A19" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="F19" s="56" t="s">
+        <v>447</v>
+      </c>
+      <c r="G19" s="57" t="s">
+        <v>448</v>
+      </c>
+      <c r="H19" s="134" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="1" customFormat="1" ht="238.5" customHeight="1">
+      <c r="A20" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="51" t="s">
         <v>425</v>
       </c>
-      <c r="E10" s="110" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="125" t="s">
-        <v>439</v>
-      </c>
-      <c r="G10" s="112" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="145" customHeight="1" thickBot="1">
-      <c r="A11" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="114" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="114" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="115" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="126" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="128" t="s">
-        <v>440</v>
-      </c>
-      <c r="G11" s="127"/>
-    </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="145" customHeight="1" thickTop="1">
-      <c r="A12" s="119" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="120" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="120" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="121" t="s">
-        <v>426</v>
-      </c>
-      <c r="E12" s="132" t="s">
-        <v>110</v>
-      </c>
-      <c r="F12" s="133" t="s">
-        <v>441</v>
-      </c>
-      <c r="G12" s="134" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="131.5" customHeight="1" thickBot="1">
-      <c r="A13" s="113" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="114" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="115" t="s">
-        <v>427</v>
-      </c>
-      <c r="E13" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="128" t="s">
-        <v>443</v>
-      </c>
-      <c r="G13" s="118" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="237" customHeight="1" thickTop="1">
-      <c r="A14" s="104" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="105" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="105" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="130" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="131" t="s">
-        <v>446</v>
-      </c>
-      <c r="G14" s="129" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="142.5" customHeight="1" thickBot="1">
-      <c r="A15" s="113" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="114" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="114" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="115" t="s">
-        <v>428</v>
-      </c>
-      <c r="E15" s="116" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="117" t="s">
-        <v>448</v>
-      </c>
-      <c r="G15" s="118"/>
-    </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="336" customHeight="1" thickTop="1">
-      <c r="A16" s="104" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" s="105" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="105" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="106" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="130" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="131" t="s">
-        <v>449</v>
-      </c>
-      <c r="G16" s="129" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="80" customHeight="1">
-      <c r="A17" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="99" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="100" t="s">
+      <c r="E20" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="56" t="s">
+        <v>451</v>
+      </c>
+      <c r="G20" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="G17" s="103"/>
-    </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="216" customHeight="1">
-      <c r="A18" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="100" t="s">
-        <v>451</v>
-      </c>
-      <c r="G18" s="103" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="175.5" customHeight="1">
-      <c r="A19" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="99" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="100" t="s">
-        <v>453</v>
-      </c>
-      <c r="G19" s="103" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="238.5" customHeight="1">
-      <c r="A20" s="36" t="s">
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1" ht="6" customHeight="1"/>
+    <row r="22" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A22" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="101"/>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
+      <c r="A23" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="B23" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="100" t="s">
-        <v>457</v>
-      </c>
-      <c r="G20" s="103" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="6" customHeight="1"/>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
-    </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
-      <c r="A23" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>152</v>
-      </c>
       <c r="C23" s="39" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D23" s="39"/>
       <c r="E23" s="39"/>
       <c r="F23" s="39" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
       <c r="A24" s="36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="73" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62"/>
+      <c r="C24" s="99" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="100"/>
+      <c r="E24" s="101"/>
       <c r="F24" s="37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A25" s="36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
+      <c r="C25" s="99" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="100"/>
+      <c r="E25" s="101"/>
       <c r="F25" s="37" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
       <c r="A26" s="36" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="73" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="61"/>
-      <c r="E26" s="62"/>
+      <c r="C26" s="99" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="100"/>
+      <c r="E26" s="101"/>
       <c r="F26" s="37" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
       <c r="A27" s="36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
+      <c r="C27" s="99" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="100"/>
+      <c r="E27" s="101"/>
       <c r="F27" s="37" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
-      <c r="A28" s="72"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-    </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="38" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
+      <c r="A28" s="97"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+    </row>
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="38.1" customHeight="1">
+      <c r="A29" s="97"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C24:E24"/>
@@ -4081,10 +4112,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -4098,31 +4125,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16" style="40" customWidth="1"/>
     <col min="2" max="2" width="36" style="40" customWidth="1"/>
     <col min="3" max="3" width="30" style="40" customWidth="1"/>
     <col min="4" max="4" width="36" style="40" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="40" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="40"/>
+    <col min="5" max="5" width="8.625" style="40" customWidth="1"/>
+    <col min="6" max="16384" width="8.625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="35" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-    </row>
-    <row r="2" spans="1:4" ht="22" customHeight="1">
-      <c r="A2" s="77" t="s">
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="105" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+    </row>
+    <row r="2" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A2" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1">
       <c r="A3" s="3"/>
@@ -4131,12 +4158,12 @@
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="76" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
+      <c r="A4" s="109" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="6" customHeight="1">
       <c r="A5" s="1"/>
@@ -4145,151 +4172,151 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A6" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
+      <c r="A6" s="106" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1" ht="38.1" customHeight="1">
+      <c r="A8" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D8" s="38" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" ht="38" customHeight="1">
-      <c r="A8" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="42" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="45" customFormat="1" ht="96" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A12" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B12" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C12" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D12" s="44" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A12" s="42" t="s">
+    <row r="13" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A13" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B13" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C13" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D13" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A13" s="42" t="s">
+    <row r="14" spans="1:4" s="2" customFormat="1" ht="110.45" customHeight="1">
+      <c r="A14" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B14" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C14" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D14" s="44" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" ht="110.5" customHeight="1">
-      <c r="A14" s="42" t="s">
+    <row r="15" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A15" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B15" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C15" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D15" s="44" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A15" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" ht="96" customHeight="1">
       <c r="A16" s="42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
@@ -4299,83 +4326,83 @@
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A18" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62"/>
+      <c r="A18" s="106" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="101"/>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A20" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="101"/>
+      <c r="D20" s="38" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A21" s="36" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A20" s="36" t="s">
+      <c r="B21" s="108" t="s">
         <v>210</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="C21" s="101"/>
+      <c r="D21" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="38" t="s">
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" ht="66.95" customHeight="1">
+      <c r="A22" s="36" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A21" s="36" t="s">
+      <c r="B22" s="108" t="s">
         <v>213</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="C22" s="101"/>
+      <c r="D22" s="38" t="s">
         <v>214</v>
-      </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="38" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" ht="67" customHeight="1">
-      <c r="A22" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="B22" s="75" t="s">
-        <v>217</v>
-      </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="38" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" ht="52.5" customHeight="1">
       <c r="A23" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="101"/>
+      <c r="D23" s="38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="90.95" customHeight="1">
+      <c r="A24" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="108" t="s">
         <v>219</v>
       </c>
-      <c r="B23" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="62"/>
-      <c r="D23" s="38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="91" customHeight="1">
-      <c r="A24" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" s="75" t="s">
-        <v>223</v>
-      </c>
-      <c r="C24" s="62"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4403,31 +4430,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
     <col min="2" max="2" width="24" style="2" customWidth="1"/>
     <col min="3" max="3" width="46" style="2" customWidth="1"/>
     <col min="4" max="4" width="34" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="2"/>
+    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="35" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>224</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" ht="22" customHeight="1">
-      <c r="A2" s="56" t="s">
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="105" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+    </row>
+    <row r="2" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1">
       <c r="A3" s="1"/>
@@ -4436,25 +4463,25 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="60" t="s">
-        <v>225</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
+      <c r="A4" s="106" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52.5" customHeight="1">
@@ -4462,13 +4489,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="52.5" customHeight="1">
@@ -4476,13 +4503,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="52.5" customHeight="1">
@@ -4490,27 +4517,27 @@
         <v>18</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="67" customHeight="1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="66.95" customHeight="1">
       <c r="A9" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="52.5" customHeight="1">
@@ -4518,13 +4545,13 @@
         <v>27</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="6" customHeight="1">
@@ -4534,123 +4561,123 @@
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A12" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="62"/>
-    </row>
-    <row r="13" spans="1:4" ht="23.5" customHeight="1">
+      <c r="A12" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+    </row>
+    <row r="13" spans="1:4" ht="23.45" customHeight="1">
       <c r="A13" s="39" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>457</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="155.1" customHeight="1">
+      <c r="A14" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>452</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>245</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>463</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="155" customHeight="1">
-      <c r="A14" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>458</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="96" customHeight="1">
       <c r="A15" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="110.45" customHeight="1">
+      <c r="A16" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="B16" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="C16" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="D16" s="37" t="s">
         <v>251</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>459</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="110.5" customHeight="1">
-      <c r="A16" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>460</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="96" customHeight="1">
       <c r="A17" s="36" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="96" customHeight="1">
       <c r="A18" s="36" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="96" customHeight="1">
       <c r="A19" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="81.599999999999994" customHeight="1">
+      <c r="A20" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="C20" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="D20" s="37" t="s">
         <v>263</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>464</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="81.5" customHeight="1">
-      <c r="A20" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>465</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="6" customHeight="1">
@@ -4659,81 +4686,81 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25" customHeight="1">
-      <c r="A22" s="60" t="s">
-        <v>466</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="62"/>
-    </row>
-    <row r="23" spans="1:4" ht="23.5" customHeight="1">
+    <row r="22" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A22" s="106" t="s">
+        <v>460</v>
+      </c>
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+    </row>
+    <row r="23" spans="1:4" ht="23.45" customHeight="1">
       <c r="A23" s="39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="39" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="67" customHeight="1">
+    <row r="24" spans="1:4" ht="66.95" customHeight="1">
       <c r="A24" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24" s="108" t="s">
+        <v>461</v>
+      </c>
+      <c r="C24" s="113"/>
+      <c r="D24" s="37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="66.95" customHeight="1">
+      <c r="A25" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" s="108" t="s">
+        <v>462</v>
+      </c>
+      <c r="C25" s="113"/>
+      <c r="D25" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="126.95" customHeight="1">
+      <c r="A26" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="B24" s="75" t="s">
-        <v>467</v>
-      </c>
-      <c r="C24" s="135"/>
-      <c r="D24" s="37" t="s">
+      <c r="B26" s="99" t="s">
+        <v>464</v>
+      </c>
+      <c r="C26" s="101"/>
+      <c r="D26" s="37" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="67" customHeight="1">
-      <c r="A25" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="B25" s="75" t="s">
-        <v>468</v>
-      </c>
-      <c r="C25" s="135"/>
-      <c r="D25" s="37" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="127" customHeight="1">
-      <c r="A26" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B26" s="136" t="s">
-        <v>470</v>
-      </c>
-      <c r="C26" s="137"/>
-      <c r="D26" s="37" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="52.5" customHeight="1">
       <c r="A27" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="B27" s="73" t="s">
-        <v>469</v>
-      </c>
-      <c r="C27" s="62"/>
+        <v>271</v>
+      </c>
+      <c r="B27" s="99" t="s">
+        <v>463</v>
+      </c>
+      <c r="C27" s="101"/>
       <c r="D27" s="37" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="37" customHeight="1">
-      <c r="A28" s="79" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="36.950000000000003" customHeight="1">
+      <c r="A28" s="111" t="s">
+        <v>273</v>
+      </c>
+      <c r="B28" s="112"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4760,46 +4787,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
     <col min="2" max="2" width="50" style="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="30" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="1"/>
+    <col min="6" max="6" width="8.625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="57"/>
-    </row>
-    <row r="2" spans="1:5" ht="22" customHeight="1">
-      <c r="A2" s="56" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="57"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="98"/>
     </row>
     <row r="3" spans="1:5" ht="6" customHeight="1"/>
-    <row r="4" spans="1:5" ht="25" customHeight="1">
-      <c r="A4" s="60" t="s">
+    <row r="4" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A4" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-    </row>
-    <row r="5" spans="1:5" ht="23.5" customHeight="1">
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+    </row>
+    <row r="5" spans="1:5" ht="23.45" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>3</v>
       </c>
@@ -4816,7 +4843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="50.5" customHeight="1">
+    <row r="6" spans="1:5" ht="50.45" customHeight="1">
       <c r="A6" s="37" t="s">
         <v>8</v>
       </c>
@@ -4833,7 +4860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="38" customHeight="1">
+    <row r="7" spans="1:5" ht="38.1" customHeight="1">
       <c r="A7" s="37" t="s">
         <v>13</v>
       </c>
@@ -4850,7 +4877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="64" customHeight="1">
+    <row r="8" spans="1:5" ht="63.95" customHeight="1">
       <c r="A8" s="37" t="s">
         <v>18</v>
       </c>
@@ -4867,7 +4894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="38" customHeight="1">
+    <row r="9" spans="1:5" ht="38.1" customHeight="1">
       <c r="A9" s="37" t="s">
         <v>23</v>
       </c>
@@ -4884,7 +4911,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="38" customHeight="1">
+    <row r="10" spans="1:5" ht="38.1" customHeight="1">
       <c r="A10" s="37" t="s">
         <v>27</v>
       </c>
@@ -4901,7 +4928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="50.5" customHeight="1">
+    <row r="11" spans="1:5" ht="50.45" customHeight="1">
       <c r="A11" s="37" t="s">
         <v>32</v>
       </c>
@@ -4918,7 +4945,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="38" customHeight="1">
+    <row r="12" spans="1:5" ht="38.1" customHeight="1">
       <c r="A12" s="37" t="s">
         <v>37</v>
       </c>
@@ -4936,16 +4963,16 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="6" customHeight="1"/>
-    <row r="14" spans="1:5" ht="25" customHeight="1">
-      <c r="A14" s="60" t="s">
+    <row r="14" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A14" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="62"/>
-    </row>
-    <row r="15" spans="1:5" ht="23.5" customHeight="1">
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="101"/>
+    </row>
+    <row r="15" spans="1:5" ht="23.45" customHeight="1">
       <c r="A15" s="39" t="s">
         <v>3</v>
       </c>
@@ -4962,7 +4989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="38" customHeight="1">
+    <row r="16" spans="1:5" ht="38.1" customHeight="1">
       <c r="A16" s="37" t="s">
         <v>8</v>
       </c>
@@ -4979,12 +5006,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="38" customHeight="1">
+    <row r="17" spans="1:5" ht="38.1" customHeight="1">
       <c r="A17" s="37" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C17" s="37" t="s">
         <v>51</v>
@@ -4996,7 +5023,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="38" customHeight="1">
+    <row r="18" spans="1:5" ht="38.1" customHeight="1">
       <c r="A18" s="37" t="s">
         <v>18</v>
       </c>
@@ -5004,64 +5031,64 @@
         <v>54</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>55</v>
+        <v>474</v>
       </c>
       <c r="D18" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="38" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="38.1" customHeight="1">
       <c r="A19" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>58</v>
+        <v>475</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="38" customHeight="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="38.1" customHeight="1">
       <c r="A20" s="37" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>61</v>
+        <v>473</v>
       </c>
       <c r="D20" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="38" customHeight="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="38.1" customHeight="1">
       <c r="A21" s="37" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>64</v>
+        <v>472</v>
       </c>
       <c r="D21" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5083,290 +5110,290 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="78" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="85" t="s">
-        <v>278</v>
-      </c>
-      <c r="B1" s="58"/>
+      <c r="A1" s="117" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="93"/>
     </row>
     <row r="2" spans="1:2" ht="30" customHeight="1">
-      <c r="A2" s="83" t="s">
-        <v>472</v>
-      </c>
-      <c r="B2" s="58"/>
+      <c r="A2" s="118" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="93"/>
     </row>
     <row r="3" spans="1:2" ht="6" customHeight="1"/>
     <row r="4" spans="1:2" ht="24" customHeight="1">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="114" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="115"/>
+    </row>
+    <row r="5" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A6" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A7" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="81"/>
-    </row>
-    <row r="5" spans="1:2" ht="37" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="B7" s="54" t="s">
         <v>280</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="37" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="37" customHeight="1">
-      <c r="A7" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="6" customHeight="1"/>
     <row r="9" spans="1:2" ht="24" customHeight="1">
-      <c r="A9" s="80" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="81"/>
-    </row>
-    <row r="10" spans="1:2" ht="20" customHeight="1">
+      <c r="A9" s="114" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="115"/>
+    </row>
+    <row r="10" spans="1:2" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="55" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B10" s="55" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="23.5" customHeight="1">
+    <row r="11" spans="1:2" ht="23.45" customHeight="1">
       <c r="A11" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="63.95" customHeight="1">
+      <c r="A12" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="50.45" customHeight="1">
+      <c r="A13" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B13" s="54" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="64" customHeight="1">
-      <c r="A12" s="53" t="s">
+    <row r="14" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A14" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B14" s="54" t="s">
         <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="50.5" customHeight="1">
-      <c r="A13" s="53" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="37" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="6" customHeight="1"/>
     <row r="16" spans="1:2" ht="24" customHeight="1">
-      <c r="A16" s="80" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="81"/>
-    </row>
-    <row r="17" spans="1:2" ht="37" customHeight="1">
-      <c r="A17" s="82" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" s="58"/>
-    </row>
-    <row r="18" spans="1:2" ht="20" customHeight="1">
+      <c r="A16" s="114" t="s">
+        <v>290</v>
+      </c>
+      <c r="B16" s="115"/>
+    </row>
+    <row r="17" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A17" s="116" t="s">
+        <v>291</v>
+      </c>
+      <c r="B17" s="93"/>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="55" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B18" s="55" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="37" customHeight="1">
+    <row r="19" spans="1:2" ht="36.950000000000003" customHeight="1">
       <c r="A19" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A20" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A21" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B21" s="54" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="37" customHeight="1">
-      <c r="A20" s="53" t="s">
-        <v>299</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="37" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>301</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1"/>
     <row r="23" spans="1:2" ht="24" customHeight="1">
-      <c r="A23" s="80" t="s">
-        <v>303</v>
-      </c>
-      <c r="B23" s="81"/>
-    </row>
-    <row r="24" spans="1:2" ht="23.5" customHeight="1">
-      <c r="A24" s="82" t="s">
-        <v>304</v>
-      </c>
-      <c r="B24" s="58"/>
-    </row>
-    <row r="25" spans="1:2" ht="20" customHeight="1">
+      <c r="A23" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="115"/>
+    </row>
+    <row r="24" spans="1:2" ht="23.45" customHeight="1">
+      <c r="A24" s="116" t="s">
+        <v>300</v>
+      </c>
+      <c r="B24" s="93"/>
+    </row>
+    <row r="25" spans="1:2" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B25" s="55" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="23.5" customHeight="1">
+    <row r="26" spans="1:2" ht="23.45" customHeight="1">
       <c r="A26" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A27" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="23.45" customHeight="1">
+      <c r="A28" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B28" s="54" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="37" customHeight="1">
-      <c r="A27" s="53" t="s">
+    <row r="29" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A29" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B29" s="54" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="23.5" customHeight="1">
-      <c r="A28" s="53" t="s">
+    <row r="30" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A30" s="119" t="s">
         <v>310</v>
       </c>
-      <c r="B28" s="54" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="37" customHeight="1">
-      <c r="A29" s="53" t="s">
-        <v>312</v>
-      </c>
-      <c r="B29" s="54" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="37" customHeight="1">
-      <c r="A30" s="84" t="s">
-        <v>314</v>
-      </c>
-      <c r="B30" s="81"/>
+      <c r="B30" s="115"/>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1"/>
     <row r="32" spans="1:2" ht="24" customHeight="1">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="114" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" s="115"/>
+    </row>
+    <row r="33" spans="1:2" ht="23.45" customHeight="1">
+      <c r="A33" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A34" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="B34" s="54" t="s">
         <v>315</v>
-      </c>
-      <c r="B32" s="81"/>
-    </row>
-    <row r="33" spans="1:2" ht="23.5" customHeight="1">
-      <c r="A33" s="53" t="s">
-        <v>316</v>
-      </c>
-      <c r="B33" s="54" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="37" customHeight="1">
-      <c r="A34" s="53" t="s">
-        <v>318</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="6" customHeight="1"/>
     <row r="36" spans="1:2" ht="24" customHeight="1">
-      <c r="A36" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="B36" s="81"/>
-    </row>
-    <row r="37" spans="1:2" ht="20" customHeight="1">
+      <c r="A36" s="114" t="s">
+        <v>316</v>
+      </c>
+      <c r="B36" s="115"/>
+    </row>
+    <row r="37" spans="1:2" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="55" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="55" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A38" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A39" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A40" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="23.45" customHeight="1">
+      <c r="A41" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" s="54" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="37" customHeight="1">
-      <c r="A38" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="B38" s="54" t="s">
+    <row r="42" spans="1:2" ht="23.45" customHeight="1">
+      <c r="A42" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="54" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="37" customHeight="1">
-      <c r="A39" s="53" t="s">
-        <v>250</v>
-      </c>
-      <c r="B39" s="54" t="s">
+    <row r="43" spans="1:2" ht="6" customHeight="1"/>
+    <row r="44" spans="1:2" ht="36.950000000000003" customHeight="1">
+      <c r="A44" s="116" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="37" customHeight="1">
-      <c r="A40" s="53" t="s">
-        <v>253</v>
-      </c>
-      <c r="B40" s="54" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="23.5" customHeight="1">
-      <c r="A41" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="B41" s="54" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="23.5" customHeight="1">
-      <c r="A42" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="B42" s="54" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="6" customHeight="1"/>
-    <row r="44" spans="1:2" ht="37" customHeight="1">
-      <c r="A44" s="82" t="s">
-        <v>327</v>
-      </c>
-      <c r="B44" s="58"/>
+      <c r="B44" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5395,279 +5422,279 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" customWidth="1"/>
+    <col min="3" max="3" width="69.875" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22" customHeight="1">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1">
+      <c r="A2" s="120" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+    </row>
+    <row r="3" spans="1:4" ht="141.94999999999999" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="11" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="86" t="s">
-        <v>330</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-    </row>
-    <row r="3" spans="1:4" ht="142" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="105" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>335</v>
-      </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
-      <c r="A5" s="86" t="s">
-        <v>336</v>
-      </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
+      <c r="A5" s="120" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
     </row>
     <row r="6" spans="1:4" ht="60" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="157.5" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="74.5" customHeight="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="74.45" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="86" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
+      <c r="A9" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
     </row>
     <row r="10" spans="1:4" ht="121.5" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="137.1" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1">
+      <c r="A12" s="120" t="s">
         <v>344</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+    </row>
+    <row r="13" spans="1:4" ht="119.1" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="137.15" customHeight="1">
-      <c r="A11" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="C13" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D13" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="152.1" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1">
-      <c r="A12" s="86" t="s">
+      <c r="D14" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-    </row>
-    <row r="13" spans="1:4" ht="119.15" customHeight="1">
-      <c r="A13" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="24" customHeight="1">
+      <c r="A15" s="120" t="s">
         <v>349</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="152.15" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1">
-      <c r="A15" s="86" t="s">
-        <v>353</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
     </row>
     <row r="16" spans="1:4" ht="105" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="158.5" customHeight="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="158.44999999999999" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="73.5" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="11" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="81.95" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="24" customHeight="1">
+      <c r="A20" s="120" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+    </row>
+    <row r="21" spans="1:4" ht="89.1" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="C21" s="14" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="82" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="D21" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="D19" s="11" t="s">
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="121" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="24" customHeight="1">
-      <c r="A20" s="86" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-    </row>
-    <row r="21" spans="1:4" ht="89.15" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="87" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5692,233 +5719,233 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="70.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="105" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.15" customHeight="1">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A1" s="124" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+    </row>
+    <row r="3" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A3" s="125" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="122" t="s">
+        <v>364</v>
+      </c>
+      <c r="B4" s="123"/>
+      <c r="C4" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="122" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-    </row>
-    <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="91" t="s">
+      <c r="B5" s="123"/>
+      <c r="C5" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="88" t="s">
+      <c r="D5" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="16" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="122" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="123"/>
+      <c r="C6" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="D6" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="122" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="16" t="s">
+      <c r="B7" s="123"/>
+      <c r="C7" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D7" s="17" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="A6" s="88" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="16" t="s">
+    <row r="8" spans="1:4" ht="30" customHeight="1">
+      <c r="A8" s="122" t="s">
         <v>373</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="A7" s="88" t="s">
+      <c r="B8" s="123"/>
+      <c r="C8" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="88" t="s">
-        <v>377</v>
-      </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="20.149999999999999" customHeight="1">
+    </row>
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22" customHeight="1">
-      <c r="A11" s="91" t="s">
-        <v>380</v>
-      </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A11" s="125" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
     </row>
     <row r="12" spans="1:4" ht="144" customHeight="1">
       <c r="A12" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="C12" s="20" t="s">
+      <c r="B13" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D12" s="11" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A14" s="125" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A13" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="19" t="s">
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+    </row>
+    <row r="15" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A15" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="B15" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22" customHeight="1">
-      <c r="A14" s="91" t="s">
+    <row r="16" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-    </row>
-    <row r="15" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A15" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="C16" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A16" s="18" t="s">
+    <row r="17" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A17" s="125" t="s">
         <v>390</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+    </row>
+    <row r="18" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C18" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22" customHeight="1">
-      <c r="A17" s="91" t="s">
+    <row r="19" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A19" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-    </row>
-    <row r="18" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A18" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="19" t="s">
+      <c r="B19" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C19" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A19" s="18" t="s">
+    <row r="20" spans="1:4" ht="138.94999999999999" customHeight="1">
+      <c r="A20" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="C20" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="D20" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="D19" s="11" t="s">
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="126" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="139" customHeight="1">
-      <c r="A20" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="92" t="s">
-        <v>405</v>
-      </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5946,235 +5973,235 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" style="23" customWidth="1"/>
     <col min="2" max="2" width="9" style="23" customWidth="1"/>
-    <col min="3" max="3" width="66.08203125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="66.125" style="23" customWidth="1"/>
     <col min="4" max="4" width="58" style="23" customWidth="1"/>
     <col min="5" max="5" width="9" style="22" customWidth="1"/>
     <col min="6" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.15" customHeight="1">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A1" s="128" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+    </row>
+    <row r="3" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A3" s="130" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="127" t="s">
+        <v>364</v>
+      </c>
+      <c r="B4" s="123"/>
+      <c r="C4" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="127" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-    </row>
-    <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="96" t="s">
+      <c r="B5" s="123"/>
+      <c r="C5" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="93" t="s">
-        <v>368</v>
-      </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="24" t="s">
+      <c r="D5" s="25" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="127" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="123"/>
+      <c r="C6" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="D6" s="25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="127" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="24" t="s">
+      <c r="B7" s="123"/>
+      <c r="C7" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="A6" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="24" t="s">
+      <c r="D7" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1">
+      <c r="A8" s="127" t="s">
         <v>373</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="A7" s="93" t="s">
+      <c r="B8" s="123"/>
+      <c r="C8" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="93" t="s">
-        <v>377</v>
-      </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="24" t="s">
-        <v>378</v>
-      </c>
       <c r="D8" s="25" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="20.149999999999999" customHeight="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="26" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22" customHeight="1">
-      <c r="A11" s="96" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A11" s="130" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+    </row>
+    <row r="12" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A12" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>380</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-    </row>
-    <row r="12" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A12" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="D12" s="30" t="s">
+      <c r="D13" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A14" s="130" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+    </row>
+    <row r="15" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A15" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>384</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A16" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A17" s="130" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+    </row>
+    <row r="18" spans="1:4" ht="95.1" customHeight="1">
+      <c r="A18" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="65.099999999999994" customHeight="1">
+      <c r="A19" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="138.94999999999999" customHeight="1">
+      <c r="A20" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="D20" s="30" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="22" customHeight="1">
-      <c r="A14" s="96" t="s">
-        <v>386</v>
-      </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-    </row>
-    <row r="15" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A16" s="27" t="s">
-        <v>390</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>391</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="22" customHeight="1">
-      <c r="A17" s="96" t="s">
-        <v>394</v>
-      </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-    </row>
-    <row r="18" spans="1:4" ht="95.15" customHeight="1">
-      <c r="A18" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="65.150000000000006" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>398</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="139" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>413</v>
-      </c>
-    </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="97" t="s">
-        <v>405</v>
-      </c>
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
+      <c r="A22" s="131" t="s">
+        <v>401</v>
+      </c>
+      <c r="B22" s="129"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="11">
